--- a/artfynd/A 9938-2026 artfynd.xlsx
+++ b/artfynd/A 9938-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122128287</v>
+        <v>122128283</v>
       </c>
       <c r="B2" t="n">
-        <v>57753</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>438668</v>
+        <v>438689</v>
       </c>
       <c r="R2" t="n">
-        <v>6243693</v>
+        <v>6243599</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,6 +788,126 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>FNT0019 Osby Östra Genastorp häckfågelinventering 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122128287</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Östra Genastorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>438668</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6243693</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Julia Björk</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Frida Nettelbladt</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>FNT0019 Osby Östra Genastorp häckfågelinventering 2024</t>
         </is>
